--- a/artfynd/A 12980-2026 artfynd.xlsx
+++ b/artfynd/A 12980-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136211418</v>
       </c>
       <c r="B4" t="n">
-        <v>104062</v>
+        <v>104065</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 12980-2026 artfynd.xlsx
+++ b/artfynd/A 12980-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136211418</v>
       </c>
       <c r="B4" t="n">
-        <v>104065</v>
+        <v>104066</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 12980-2026 artfynd.xlsx
+++ b/artfynd/A 12980-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136211417</v>
       </c>
       <c r="B2" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136211415</v>
       </c>
       <c r="B3" t="n">
-        <v>58709</v>
+        <v>58711</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136211418</v>
       </c>
       <c r="B4" t="n">
-        <v>104066</v>
+        <v>104071</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 12980-2026 artfynd.xlsx
+++ b/artfynd/A 12980-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136211418</v>
       </c>
       <c r="B4" t="n">
-        <v>104071</v>
+        <v>104073</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
